--- a/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -3260,7 +3260,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>82</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>94</v>

--- a/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -877,8 +877,7 @@
 </t>
   </si>
   <si>
-    <t>参照されるイベントの一部分
-【JP Core仕様】未使用</t>
+    <t>参照されるイベントの一部分 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>ObservationをEncounterにencounter要素を使ってリンクする。もうひとつ別のObservationを参照することについては、以降にあるt [Notes](observation.html#obsgrouping)　をガイダンスとして参照のこと。</t>
@@ -896,8 +895,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>結果の状態  
-【JP Core仕様】ステータス</t>
+    <t>結果の状態 【JP Core仕様】ステータス</t>
   </si>
   <si>
     <t>このリソースは現在有効でないというマークをするコードを含んでいるため、この要素はモディファイアー（修飾的要素）として位置づけられている。</t>
@@ -1243,8 +1241,7 @@
 </t>
   </si>
   <si>
-    <t>観察対象者  
-【JP Core仕様】患者情報</t>
+    <t>観察対象者 【JP Core仕様】患者情報</t>
   </si>
   <si>
     <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明なデバイスによって観察が行われるケースである。この場合、観察は何らかのコンテキスト/チャネルマッチング技術を介して患者にマッチングされる必要があり、患者にマッチングされれば、その時点で本要素を更新する必要がある。</t>
@@ -1272,8 +1269,7 @@
 </t>
   </si>
   <si>
-    <t>subject 要素が実際のobservationの対象でない場合に、observation の対象物。  
-【JP Core仕様】未使用</t>
+    <t>subject 要素が実際のobservationの対象でない場合に、observation の対象物。 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>T通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
@@ -1325,8 +1321,7 @@
 </t>
   </si>
   <si>
-    <t>臨床的に関連する時刻または時間  
-【JP Core仕様】実施日時</t>
+    <t>臨床的に関連する時刻または時間 【JP Core仕様】実施日時</t>
   </si>
   <si>
     <t>この観察結果が過去の報告でない限り、少なくとも日付が存在する必要がある。不正確または「あいまいな」時間を記録するには（たとえば、「朝食後」に行われた血糖測定）、[Timing]（datatypes.html＃timing）データ型を使用して、測定を通常のライフイベントに関連付けることができる。</t>
@@ -1354,8 +1349,7 @@
 </t>
   </si>
   <si>
-    <t>このバージョンが利用可能となった日時  
-【JP Core仕様】所見確定日時</t>
+    <t>このバージョンが利用可能となった日時 【JP Core仕様】所見確定日時</t>
   </si>
   <si>
     <t>レビューと検証を必要としないobservationの場合、リソース自体の[`lastUpdated`]（resource-definitions.html＃Meta.lastUpdated）日時と同じになる場合がある。特定の更新のレビューと検証が必要なobservationの場合、新しいバージョンを再度レビューして検証する必要がないような臨床的に重要でない更新がなされたために、リソース自体の「lastUpdated」時間はこれと異なる場合がある。</t>
@@ -1401,8 +1395,7 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>実際の結果値  
-【JP Core仕様】特定の歯の有無</t>
+    <t>実際の結果値 【JP Core仕様】特定の歯の有無</t>
   </si>
   <si>
     <t>観察にはあります。1）ここでの単一の値、2）関連する値とコンポーネント値のセット、または3）関連またはコンポーネント値のセットのみ。値が存在する場合、この要素のデータ型は、viscervation.codeによって決定する必要があります。フィールドが通常コーディングされている場合、または観測に関連付けられたタイプの場合、文字列の代わりにテキストのみを持つCodeableconecteが使用されます。コードはコード化された値を定義します。追加のガイダンスについては、以下の[[メモ]セクション]（[観察.html＃注）を参照してください。 / An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
@@ -1433,8 +1426,7 @@
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
-    <t>結果が欠損値である理由
-【JP Core仕様】結果が存在しなかった場合、その理由</t>
+    <t>結果が欠損値である理由 【JP Core仕様】結果が存在しなかった場合、その理由</t>
   </si>
   <si>
     <t>ヌル値または例外値は、FHIRオブザベーションで2つの方法で表すことができる。 1つの方法は、それらを値セットに含めて、値の例外を表す方法である。たとえば、血清学的検査の測定値は、「検出された」、「検出されなかった」、「決定的でない」、または「検体が不十分」である可能性がある。別の方法は、実際の観測にvalue要素を使用し、明示的なdataAbsentReason要素を使用して例外的な値を記録することである。たとえば、測定が完了しなかった場合、dataAbsentReasonコード「error」を使用できる。この場合には、観測値は、報告する値がある場合にのみ報告される可能性があることに注意する必要がある。たとえば、差分セルカウント値は&gt; 0の場合にのみ報告される場合がある。これらのオプションのため、nullまたは例外値の一般的な観測値を解釈するにはユースケースの合意が必要である。</t>
@@ -1466,8 +1458,7 @@
 </t>
   </si>
   <si>
-    <t>高、低、正常等の結果のカテゴリ分けした評価
-【JP Core仕様】未使用</t>
+    <t>高、低、正常等の結果のカテゴリ分けした評価 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>「異常フラグ」として呼ばれる検査結果解釈コードが従来から使用されており、その使用はコード化された解釈が関連するような他の場合でも拡大して使われている。多くの場合、1つ以上の単純でコンパクトなコードとして報告され、この要素は、結果の意味や正常かどうかを示すために、レポートや時系列表で結果値の隣に配置されることがよくある。</t>
@@ -1501,8 +1492,7 @@
 </t>
   </si>
   <si>
-    <t>結果に対するコメント  
-【JP Core仕様】未使用</t>
+    <t>結果に対するコメント 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>観察（結果）に関する一般的な記述、重要な、予期しない、または信頼できない結果値に関する記述、またはその解釈に関連する場合はそのソースに関する情報が含まれる場合がある。</t>
@@ -1521,8 +1511,7 @@
     <t>Observation.bodySite</t>
   </si>
   <si>
-    <t>観察された身体部位  
-【JP Core仕様】特定の歯（歯式）を指定</t>
+    <t>観察された身体部位 【JP Core仕様】特定の歯（歯式）を指定</t>
   </si>
   <si>
     <t>観察結果で見つかったコードで暗黙的ではない場合にのみ使用されます。多くのシステムでは、これはインラインコンポーネントの代わりに関連する観察として表される場合があります。
@@ -1576,8 +1565,7 @@
 </t>
   </si>
   <si>
-    <t>観察（観測、検査）に使われた検体材料
-【JP Core仕様】未使用</t>
+    <t>観察（観測、検査）に使われた検体材料 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>`Observation.code`にあるコードで暗黙的に示されない場合にのみ使用する必要がある。検体自体の観察は行われない。観察（観測、検査）対象者に対して実施されるが、多くの場合には対象者から得られた検体に対して実施される。検体が奥の場合に関わるが、それらは常に追跡され、明示的に報告されるとは限らないことに注意すること。またobservationリソースは、検体を明示的に記述するような状況下（診断レポートなど）で使用される場合があることに注意。</t>
@@ -1797,8 +1785,7 @@
 </t>
   </si>
   <si>
-    <t>observationグループに属する関連リソース
-【JP Core仕様】現存歯もしくは欠損歯に対応する処置状態のObservationリソースを参照</t>
+    <t>observationグループに属する関連リソース 【JP Core仕様】現存歯もしくは欠損歯に対応する処置状態のObservationリソースを参照</t>
   </si>
   <si>
     <t>この要素を使用する場合、observationには通常、値または関連するリソースのセットのいずれかを含む。その両方を含む場合もある。複数のobservationをグループに一緒にまとめる方法については、以下の[メモ]（observation.html＃obsgrouping）を参照せよ。システムは、[QuestionnaireResponse]（questionnaireresponse.html）からの結果を計算して最終スコアにし、そのスコアをobservationとして表す場合があることに注意。</t>
@@ -1817,8 +1804,7 @@
 </t>
   </si>
   <si>
-    <t>observationの発生源に関連する測定
-【JP Core仕様】未使用</t>
+    <t>observationの発生源に関連する測定 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>この要素にリストされているすべての参照の選択肢は、派生値の元のデータなる可能性のある臨床観察やその他の測定値を表すことができる。最も一般的な参照先は、別のobservationである。observationをグループに一緒にまとめる方法については、以下の[メモ]（observation.html＃obsgrouping）を参照すること。</t>
@@ -1830,8 +1816,7 @@
     <t>Observation.component</t>
   </si>
   <si>
-    <t>複合的な結果
-【JP Core仕様】未使用</t>
+    <t>複合的な結果 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>複数のObservation をグループに一緒にまとめる方法については、以下の[Notes]（observation.html＃notes）を参照すること。</t>
@@ -13503,7 +13488,7 @@
         <v>81</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>83</v>
